--- a/main/ig/documentReferenceToPDSM.xlsx
+++ b/main/ig/documentReferenceToPDSM.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="88">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T07:22:41+00:00</t>
+    <t>2026-09-24T12:10:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -117,13 +117,7 @@
     <t>equivalent</t>
   </si>
   <si>
-    <t>DocumentReference.id</t>
-  </si>
-  <si>
-    <t>DocumentEntry.logicalId</t>
-  </si>
-  <si>
-    <t>DocumentReference.identifier</t>
+    <t>DocumentReference.identifier:entryUUID</t>
   </si>
   <si>
     <t>DocumentEntry.mimeType</t>
@@ -183,13 +177,13 @@
     <t>DocumentEntry.sourcePatientID</t>
   </si>
   <si>
-    <t>DocumentReference.subject.fr-core-patient</t>
+    <t>DocumentReference.context.sourcePatientInfo.identifier</t>
   </si>
   <si>
     <t>DocumentEntry.sourcePatientInfo</t>
   </si>
   <si>
-    <t>DocumentReference.context.sourcePatientInfo</t>
+    <t>DocumentReference.context.sourcePatientInfo.reference</t>
   </si>
   <si>
     <t>DocumentEntry.URI</t>
@@ -210,9 +204,15 @@
     <t>DocumentEntry.patientID</t>
   </si>
   <si>
+    <t>DocumentReference.subject</t>
+  </si>
+  <si>
     <t>DocumentEntry.uniqueId</t>
   </si>
   <si>
+    <t>DocumentReference.masterIdentifier</t>
+  </si>
+  <si>
     <t>DocumentEntry.class</t>
   </si>
   <si>
@@ -258,13 +258,25 @@
     <t>DocumentEntry.creationTime</t>
   </si>
   <si>
-    <t>DocumentReference.date</t>
+    <t>DocumentReference.content.attachment.creation</t>
   </si>
   <si>
     <t>DocumentEntry.referenceIdList</t>
   </si>
   <si>
     <t>DocumentReference.context.related:referenceIdList</t>
+  </si>
+  <si>
+    <t>DocumentEntry.author</t>
+  </si>
+  <si>
+    <t>DocumentReference.author</t>
+  </si>
+  <si>
+    <t>DocumentEntry.version</t>
+  </si>
+  <si>
+    <t>DocumentReference.meta.versionId</t>
   </si>
 </sst>
 </file>
@@ -520,7 +532,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -589,11 +601,9 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D5" t="s" s="2">
         <v>38</v>
       </c>
+      <c r="D5" s="2"/>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
@@ -602,9 +612,11 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s" s="2">
         <v>40</v>
       </c>
-      <c r="D6" s="2"/>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
@@ -652,7 +664,7 @@
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>48</v>
@@ -665,7 +677,7 @@
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>50</v>
@@ -717,23 +729,23 @@
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="E16" s="2"/>
     </row>
@@ -772,139 +784,152 @@
         <v>33</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E29" s="2"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="D30" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="E30" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
